--- a/original/it/italian_talking_clock_audio_list.xlsx
+++ b/original/it/italian_talking_clock_audio_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Language</t>
   </si>
@@ -31,37 +31,148 @@
     <t>Italian</t>
   </si>
   <si>
-    <t>e_la.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">è la</t>
-  </si>
-  <si>
-    <t>sono_le.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sono le</t>
-  </si>
-  <si>
-    <t>e.mp3</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>una.mp3</t>
-  </si>
-  <si>
-    <t>una</t>
-  </si>
-  <si>
-    <t>e_mezzanotte.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e mezzanotte</t>
-  </si>
-  <si>
-    <t>English</t>
+    <t>0h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E mezzanotte</t>
+  </si>
+  <si>
+    <t>1h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E la una</t>
+  </si>
+  <si>
+    <t>2h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 2</t>
+  </si>
+  <si>
+    <t>3h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 3</t>
+  </si>
+  <si>
+    <t>4h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 4</t>
+  </si>
+  <si>
+    <t>5h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 5</t>
+  </si>
+  <si>
+    <t>6h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 6</t>
+  </si>
+  <si>
+    <t>7h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 7</t>
+  </si>
+  <si>
+    <t>8h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 8</t>
+  </si>
+  <si>
+    <t>9h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 9</t>
+  </si>
+  <si>
+    <t>10h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 10</t>
+  </si>
+  <si>
+    <t>11h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 11</t>
+  </si>
+  <si>
+    <t>12h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 12</t>
+  </si>
+  <si>
+    <t>13h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 13</t>
+  </si>
+  <si>
+    <t>14h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 14</t>
+  </si>
+  <si>
+    <t>15h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 15</t>
+  </si>
+  <si>
+    <t>16h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 16</t>
+  </si>
+  <si>
+    <t>17h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 17</t>
+  </si>
+  <si>
+    <t>18h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 18</t>
+  </si>
+  <si>
+    <t>19h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 19</t>
+  </si>
+  <si>
+    <t>20h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 20</t>
+  </si>
+  <si>
+    <t>21h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 21</t>
+  </si>
+  <si>
+    <t>22h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 22</t>
+  </si>
+  <si>
+    <t>23h.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono le 23</t>
   </si>
   <si>
     <t>battery_it.mp3</t>
@@ -680,10 +791,10 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -691,10 +802,10 @@
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -702,10 +813,10 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -713,15 +824,15 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -735,276 +846,257 @@
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="str">
-        <f t="shared" ref="B7:B10" si="0">_xlfn.CONCAT(C7,".mp3")</f>
-        <v>1.mp3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="15">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="15">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="15">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="15">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="15">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="15">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="15">
+      <c r="A14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" ht="15">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" ht="15">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="15">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="15">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" ht="15">
+      <c r="A19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" ht="15">
+      <c r="A20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" ht="15">
+      <c r="A21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="15">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" ht="15">
+      <c r="A23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" ht="15">
+      <c r="A24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" ht="15">
+      <c r="A25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" ht="15">
+      <c r="A26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <f t="shared" ref="B26:B29" si="0">_xlfn.CONCAT(C26,".mp3")</f>
+        <v>1.mp3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="15">
+      <c r="A27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2.mp3</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C27" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="15">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="str">
+    <row r="28" ht="15">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3.mp3</v>
       </c>
-      <c r="C9" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="15">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="str">
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="15">
+      <c r="A29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4.mp3</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C29" s="1">
         <v>4</v>
-      </c>
-    </row>
-    <row r="11" ht="15">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <f t="shared" ref="B11:B65" si="1">_xlfn.CONCAT(C11,".mp3")</f>
-        <v>5.mp3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" ht="15">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>6.mp3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" ht="15">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>7.mp3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" ht="15">
-      <c r="A14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>8.mp3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="15">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>9.mp3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" ht="15">
-      <c r="A16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>10.mp3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" ht="15">
-      <c r="A17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>11.mp3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" ht="15">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>12.mp3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="15">
-      <c r="A19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>13.mp3</v>
-      </c>
-      <c r="C19" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="15">
-      <c r="A20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>14.mp3</v>
-      </c>
-      <c r="C20" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" ht="15">
-      <c r="A21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>15.mp3</v>
-      </c>
-      <c r="C21" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" ht="15">
-      <c r="A22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>16.mp3</v>
-      </c>
-      <c r="C22" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" ht="15">
-      <c r="A23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>17.mp3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="15">
-      <c r="A24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>18.mp3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" ht="15">
-      <c r="A25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>19.mp3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" ht="15">
-      <c r="A26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>20.mp3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="15">
-      <c r="A27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>21.mp3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" ht="15">
-      <c r="A28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>22.mp3</v>
-      </c>
-      <c r="C28" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" ht="15">
-      <c r="A29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>23.mp3</v>
-      </c>
-      <c r="C29" s="1">
-        <v>23</v>
       </c>
     </row>
     <row r="30" ht="15">
@@ -1012,11 +1104,11 @@
         <v>3</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>24.mp3</v>
+        <f t="shared" ref="B30:B84" si="1">_xlfn.CONCAT(C30,".mp3")</f>
+        <v>5.mp3</v>
       </c>
       <c r="C30" s="1">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" ht="15">
@@ -1025,10 +1117,10 @@
       </c>
       <c r="B31" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>25.mp3</v>
+        <v>6.mp3</v>
       </c>
       <c r="C31" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" ht="15">
@@ -1037,10 +1129,10 @@
       </c>
       <c r="B32" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>26.mp3</v>
+        <v>7.mp3</v>
       </c>
       <c r="C32" s="1">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" ht="15">
@@ -1049,10 +1141,10 @@
       </c>
       <c r="B33" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>27.mp3</v>
+        <v>8.mp3</v>
       </c>
       <c r="C33" s="1">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" ht="15">
@@ -1061,10 +1153,10 @@
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>28.mp3</v>
+        <v>9.mp3</v>
       </c>
       <c r="C34" s="1">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" ht="15">
@@ -1073,10 +1165,10 @@
       </c>
       <c r="B35" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>29.mp3</v>
+        <v>10.mp3</v>
       </c>
       <c r="C35" s="1">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="15">
@@ -1085,10 +1177,10 @@
       </c>
       <c r="B36" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>30.mp3</v>
+        <v>11.mp3</v>
       </c>
       <c r="C36" s="1">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" ht="15">
@@ -1097,10 +1189,10 @@
       </c>
       <c r="B37" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>31.mp3</v>
+        <v>12.mp3</v>
       </c>
       <c r="C37" s="1">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" ht="15">
@@ -1109,10 +1201,10 @@
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>32.mp3</v>
+        <v>13.mp3</v>
       </c>
       <c r="C38" s="1">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" ht="15">
@@ -1121,10 +1213,10 @@
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>33.mp3</v>
+        <v>14.mp3</v>
       </c>
       <c r="C39" s="1">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" ht="15">
@@ -1133,10 +1225,10 @@
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>34.mp3</v>
+        <v>15.mp3</v>
       </c>
       <c r="C40" s="1">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" ht="15">
@@ -1145,10 +1237,10 @@
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>35.mp3</v>
+        <v>16.mp3</v>
       </c>
       <c r="C41" s="1">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" ht="15">
@@ -1157,10 +1249,10 @@
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>36.mp3</v>
+        <v>17.mp3</v>
       </c>
       <c r="C42" s="1">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" ht="15">
@@ -1169,10 +1261,10 @@
       </c>
       <c r="B43" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>37.mp3</v>
+        <v>18.mp3</v>
       </c>
       <c r="C43" s="1">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" ht="15">
@@ -1181,10 +1273,10 @@
       </c>
       <c r="B44" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>38.mp3</v>
+        <v>19.mp3</v>
       </c>
       <c r="C44" s="1">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" ht="15">
@@ -1193,10 +1285,10 @@
       </c>
       <c r="B45" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>39.mp3</v>
+        <v>20.mp3</v>
       </c>
       <c r="C45" s="1">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" ht="15">
@@ -1205,10 +1297,10 @@
       </c>
       <c r="B46" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>40.mp3</v>
+        <v>21.mp3</v>
       </c>
       <c r="C46" s="1">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" ht="15">
@@ -1217,10 +1309,10 @@
       </c>
       <c r="B47" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>41.mp3</v>
+        <v>22.mp3</v>
       </c>
       <c r="C47" s="1">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" ht="15">
@@ -1229,10 +1321,10 @@
       </c>
       <c r="B48" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>42.mp3</v>
+        <v>23.mp3</v>
       </c>
       <c r="C48" s="1">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" ht="15">
@@ -1241,10 +1333,10 @@
       </c>
       <c r="B49" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>43.mp3</v>
+        <v>24.mp3</v>
       </c>
       <c r="C49" s="1">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" ht="15">
@@ -1253,10 +1345,10 @@
       </c>
       <c r="B50" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>44.mp3</v>
+        <v>25.mp3</v>
       </c>
       <c r="C50" s="1">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" ht="15">
@@ -1265,10 +1357,10 @@
       </c>
       <c r="B51" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>45.mp3</v>
+        <v>26.mp3</v>
       </c>
       <c r="C51" s="1">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" ht="15">
@@ -1277,10 +1369,10 @@
       </c>
       <c r="B52" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>46.mp3</v>
+        <v>27.mp3</v>
       </c>
       <c r="C52" s="1">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" ht="15">
@@ -1289,10 +1381,10 @@
       </c>
       <c r="B53" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>47.mp3</v>
+        <v>28.mp3</v>
       </c>
       <c r="C53" s="1">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" ht="15">
@@ -1301,10 +1393,10 @@
       </c>
       <c r="B54" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>48.mp3</v>
+        <v>29.mp3</v>
       </c>
       <c r="C54" s="1">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" ht="15">
@@ -1313,10 +1405,10 @@
       </c>
       <c r="B55" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>49.mp3</v>
+        <v>30.mp3</v>
       </c>
       <c r="C55" s="1">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" ht="15">
@@ -1325,10 +1417,10 @@
       </c>
       <c r="B56" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>50.mp3</v>
+        <v>31.mp3</v>
       </c>
       <c r="C56" s="1">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" ht="15">
@@ -1337,10 +1429,10 @@
       </c>
       <c r="B57" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>51.mp3</v>
+        <v>32.mp3</v>
       </c>
       <c r="C57" s="1">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" ht="15">
@@ -1349,10 +1441,10 @@
       </c>
       <c r="B58" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>52.mp3</v>
+        <v>33.mp3</v>
       </c>
       <c r="C58" s="1">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" ht="15">
@@ -1361,10 +1453,10 @@
       </c>
       <c r="B59" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>53.mp3</v>
+        <v>34.mp3</v>
       </c>
       <c r="C59" s="1">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" ht="15">
@@ -1373,10 +1465,10 @@
       </c>
       <c r="B60" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>54.mp3</v>
+        <v>35.mp3</v>
       </c>
       <c r="C60" s="1">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" ht="15">
@@ -1385,10 +1477,10 @@
       </c>
       <c r="B61" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>55.mp3</v>
+        <v>36.mp3</v>
       </c>
       <c r="C61" s="1">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" ht="15">
@@ -1397,10 +1489,10 @@
       </c>
       <c r="B62" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>56.mp3</v>
+        <v>37.mp3</v>
       </c>
       <c r="C62" s="1">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" ht="15">
@@ -1409,10 +1501,10 @@
       </c>
       <c r="B63" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>57.mp3</v>
+        <v>38.mp3</v>
       </c>
       <c r="C63" s="1">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" ht="15">
@@ -1421,10 +1513,10 @@
       </c>
       <c r="B64" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>58.mp3</v>
+        <v>39.mp3</v>
       </c>
       <c r="C64" s="1">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" ht="15">
@@ -1433,183 +1525,316 @@
       </c>
       <c r="B65" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>59.mp3</v>
+        <v>40.mp3</v>
       </c>
       <c r="C65" s="1">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" ht="15">
       <c r="A66" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="B66" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>41.mp3</v>
+      </c>
+      <c r="C66" s="1">
+        <v>41</v>
       </c>
     </row>
     <row r="67" ht="15">
       <c r="A67" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="B67" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>42.mp3</v>
+      </c>
+      <c r="C67" s="1">
+        <v>42</v>
       </c>
     </row>
     <row r="68" ht="15">
       <c r="A68" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="B68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>43.mp3</v>
+      </c>
+      <c r="C68" s="1">
+        <v>43</v>
       </c>
     </row>
     <row r="69" ht="15">
       <c r="A69" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="B69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>44.mp3</v>
+      </c>
+      <c r="C69" s="1">
+        <v>44</v>
       </c>
     </row>
     <row r="70" ht="15">
       <c r="A70" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>45.mp3</v>
+      </c>
+      <c r="C70" s="1">
+        <v>45</v>
       </c>
     </row>
     <row r="71" ht="15">
       <c r="A71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="B71" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>46.mp3</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46</v>
       </c>
     </row>
     <row r="72" ht="15">
       <c r="A72" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="B72" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>47.mp3</v>
+      </c>
+      <c r="C72" s="1">
+        <v>47</v>
       </c>
     </row>
     <row r="73" ht="15">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
+      <c r="A73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>48.mp3</v>
+      </c>
+      <c r="C73" s="1">
+        <v>48</v>
+      </c>
     </row>
     <row r="74" ht="15">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
+      <c r="A74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>49.mp3</v>
+      </c>
+      <c r="C74" s="1">
+        <v>49</v>
+      </c>
     </row>
     <row r="75" ht="15">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
+      <c r="A75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>50.mp3</v>
+      </c>
+      <c r="C75" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="76" ht="15">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
+      <c r="A76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>51.mp3</v>
+      </c>
+      <c r="C76" s="1">
+        <v>51</v>
+      </c>
     </row>
     <row r="77" ht="15">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
+      <c r="A77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>52.mp3</v>
+      </c>
+      <c r="C77" s="1">
+        <v>52</v>
+      </c>
     </row>
     <row r="78" ht="15">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
+      <c r="A78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>53.mp3</v>
+      </c>
+      <c r="C78" s="1">
+        <v>53</v>
+      </c>
     </row>
     <row r="79" ht="15">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
+      <c r="A79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>54.mp3</v>
+      </c>
+      <c r="C79" s="1">
+        <v>54</v>
+      </c>
     </row>
     <row r="80" ht="15">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
+      <c r="A80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>55.mp3</v>
+      </c>
+      <c r="C80" s="1">
+        <v>55</v>
+      </c>
     </row>
     <row r="81" ht="15">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
+      <c r="A81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>56.mp3</v>
+      </c>
+      <c r="C81" s="1">
+        <v>56</v>
+      </c>
     </row>
     <row r="82" ht="15">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
+      <c r="A82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>57.mp3</v>
+      </c>
+      <c r="C82" s="1">
+        <v>57</v>
+      </c>
     </row>
     <row r="83" ht="15">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>58.mp3</v>
+      </c>
+      <c r="C83" s="1">
+        <v>58</v>
+      </c>
     </row>
     <row r="84" ht="15">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
+      <c r="A84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>59.mp3</v>
+      </c>
+      <c r="C84" s="1">
+        <v>59</v>
+      </c>
     </row>
     <row r="85" ht="15">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
+      <c r="A85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="86" ht="15">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
+      <c r="A86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="87" ht="15">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
+      <c r="A87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="88" ht="15">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
+      <c r="A88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="89" ht="15">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
+      <c r="A89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="90" ht="15">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
+      <c r="A90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="91" ht="15">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
+      <c r="A91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="92" ht="15">
       <c r="A92" s="1"/>
@@ -1633,48 +1858,143 @@
     </row>
     <row r="96" ht="15">
       <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
     </row>
     <row r="97" ht="15">
       <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
     </row>
     <row r="98" ht="15">
       <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
     </row>
     <row r="99" ht="15">
       <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
     </row>
     <row r="100" ht="15">
       <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
     </row>
     <row r="101" ht="15">
       <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
     </row>
     <row r="102" ht="15">
       <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
     </row>
     <row r="103" ht="15">
       <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
     </row>
     <row r="104" ht="15">
       <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
     </row>
     <row r="105" ht="15">
       <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
     </row>
     <row r="106" ht="15">
       <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
     </row>
     <row r="107" ht="15">
       <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
     </row>
     <row r="108" ht="15">
       <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
     </row>
     <row r="109" ht="15">
       <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
     </row>
     <row r="110" ht="15">
       <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+    </row>
+    <row r="111" ht="15">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+    </row>
+    <row r="112" ht="15">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+    </row>
+    <row r="113" ht="15">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+    </row>
+    <row r="114" ht="15">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+    </row>
+    <row r="115" ht="15">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" ht="15">
+      <c r="A116" s="1"/>
+    </row>
+    <row r="117" ht="15">
+      <c r="A117" s="1"/>
+    </row>
+    <row r="118" ht="15">
+      <c r="A118" s="1"/>
+    </row>
+    <row r="119" ht="15">
+      <c r="A119" s="1"/>
+    </row>
+    <row r="120" ht="15">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="121" ht="15">
+      <c r="A121" s="1"/>
+    </row>
+    <row r="122" ht="15">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="123" ht="15">
+      <c r="A123" s="1"/>
+    </row>
+    <row r="124" ht="15">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" ht="15">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" ht="15">
+      <c r="A126" s="1"/>
+    </row>
+    <row r="127" ht="15">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="128" ht="15">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" ht="15">
+      <c r="A129" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
